--- a/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AV21"/>
+  <dimension ref="A2:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,10 @@
     <col width="9" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
-    <col width="46" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="48" max="48"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="46" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -599,8 +602,11 @@
       <c r="AP3" s="3" t="n">
         <v>46276</v>
       </c>
-      <c r="AS3" s="4" t="n">
+      <c r="AS3" s="3" t="n">
         <v>46283</v>
+      </c>
+      <c r="AV3" s="4" t="n">
+        <v>46290</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -826,22 +832,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AS4" s="6" t="inlineStr">
+      <c r="AS4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AT4" s="6" t="inlineStr">
+      <c r="AT4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AU4" s="6" t="inlineStr">
+      <c r="AU4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AV4" s="5" t="inlineStr">
+      <c r="AV4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AW4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AX4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -900,6 +921,9 @@
       <c r="AT5" s="8" t="n"/>
       <c r="AU5" s="8" t="n"/>
       <c r="AV5" s="8" t="n"/>
+      <c r="AW5" s="8" t="n"/>
+      <c r="AX5" s="8" t="n"/>
+      <c r="AY5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1061,20 +1085,31 @@
         <f>AQ6/$D$6</f>
         <v/>
       </c>
-      <c r="AS6" s="14">
+      <c r="AS6" s="12">
         <f>AT6-AQ6</f>
         <v/>
       </c>
-      <c r="AT6" s="14" t="n">
+      <c r="AT6" s="12" t="n">
         <v>317</v>
       </c>
-      <c r="AU6" s="15">
+      <c r="AU6" s="13">
         <f>AT6/$D$6</f>
         <v/>
       </c>
-      <c r="AV6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 194 units, Block B: 123 units</t>
+      <c r="AV6" s="14">
+        <f>AW6-AT6</f>
+        <v/>
+      </c>
+      <c r="AW6" s="14" t="n">
+        <v>321</v>
+      </c>
+      <c r="AX6" s="15">
+        <f>AW6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 195 units, Block B: 126 units</t>
         </is>
       </c>
     </row>
@@ -1238,20 +1273,31 @@
         <f>AQ7/$D$7</f>
         <v/>
       </c>
-      <c r="AS7" s="14">
+      <c r="AS7" s="12">
         <f>AT7-AQ7</f>
         <v/>
       </c>
-      <c r="AT7" s="14" t="n">
+      <c r="AT7" s="12" t="n">
         <v>993</v>
       </c>
-      <c r="AU7" s="15">
+      <c r="AU7" s="13">
         <f>AT7/$D$7</f>
         <v/>
       </c>
-      <c r="AV7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 409 units, Block B: 386 units, Block C: 89 units, Block D: 109 units</t>
+      <c r="AV7" s="14">
+        <f>AW7-AT7</f>
+        <v/>
+      </c>
+      <c r="AW7" s="14" t="n">
+        <v>1007</v>
+      </c>
+      <c r="AX7" s="15">
+        <f>AW7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 415 units, Block B: 391 units, Block C: 91 units, Block D: 110 units</t>
         </is>
       </c>
     </row>
@@ -1415,18 +1461,29 @@
         <f>AQ8/$D$8</f>
         <v/>
       </c>
-      <c r="AS8" s="14">
+      <c r="AS8" s="12">
         <f>AT8-AQ8</f>
         <v/>
       </c>
-      <c r="AT8" s="14" t="n">
+      <c r="AT8" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="AU8" s="15">
+      <c r="AU8" s="13">
         <f>AT8/$D$8</f>
         <v/>
       </c>
-      <c r="AV8" s="10" t="inlineStr">
+      <c r="AV8" s="14">
+        <f>AW8-AT8</f>
+        <v/>
+      </c>
+      <c r="AW8" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="AX8" s="15">
+        <f>AW8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1592,20 +1649,31 @@
         <f>AQ9/$D$9</f>
         <v/>
       </c>
-      <c r="AS9" s="14">
+      <c r="AS9" s="12">
         <f>AT9-AQ9</f>
         <v/>
       </c>
-      <c r="AT9" s="14" t="n">
+      <c r="AT9" s="12" t="n">
         <v>1076</v>
       </c>
-      <c r="AU9" s="15">
+      <c r="AU9" s="13">
         <f>AT9/$D$9</f>
         <v/>
       </c>
-      <c r="AV9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 670 units, Phase 2: 406 units</t>
+      <c r="AV9" s="14">
+        <f>AW9-AT9</f>
+        <v/>
+      </c>
+      <c r="AW9" s="14" t="n">
+        <v>1086</v>
+      </c>
+      <c r="AX9" s="15">
+        <f>AW9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 415 units</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1730,9 @@
       <c r="AT10" s="8" t="n"/>
       <c r="AU10" s="8" t="n"/>
       <c r="AV10" s="8" t="n"/>
+      <c r="AW10" s="8" t="n"/>
+      <c r="AX10" s="8" t="n"/>
+      <c r="AY10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1823,18 +1894,29 @@
         <f>AQ11/$D$11</f>
         <v/>
       </c>
-      <c r="AS11" s="14">
+      <c r="AS11" s="12">
         <f>AT11-AQ11</f>
         <v/>
       </c>
-      <c r="AT11" s="14" t="n">
+      <c r="AT11" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="AU11" s="15">
+      <c r="AU11" s="13">
         <f>AT11/$D$11</f>
         <v/>
       </c>
-      <c r="AV11" s="10" t="inlineStr">
+      <c r="AV11" s="14">
+        <f>AW11-AT11</f>
+        <v/>
+      </c>
+      <c r="AW11" s="14" t="n">
+        <v>845</v>
+      </c>
+      <c r="AX11" s="15">
+        <f>AW11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2000,20 +2082,31 @@
         <f>AQ12/$D$12</f>
         <v/>
       </c>
-      <c r="AS12" s="14">
+      <c r="AS12" s="12">
         <f>AT12-AQ12</f>
         <v/>
       </c>
-      <c r="AT12" s="14" t="n">
+      <c r="AT12" s="12" t="n">
         <v>1542</v>
       </c>
-      <c r="AU12" s="15">
+      <c r="AU12" s="13">
         <f>AT12/$D$12</f>
         <v/>
       </c>
-      <c r="AV12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 520 units, Block B: 535 units, Block D: 487 units</t>
+      <c r="AV12" s="14">
+        <f>AW12-AT12</f>
+        <v/>
+      </c>
+      <c r="AW12" s="14" t="n">
+        <v>1559</v>
+      </c>
+      <c r="AX12" s="15">
+        <f>AW12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 527 units, Block B: 538 units, Block D: 494 units</t>
         </is>
       </c>
     </row>
@@ -2177,20 +2270,31 @@
         <f>AQ13/$D$13</f>
         <v/>
       </c>
-      <c r="AS13" s="14">
+      <c r="AS13" s="12">
         <f>AT13-AQ13</f>
         <v/>
       </c>
-      <c r="AT13" s="14" t="n">
+      <c r="AT13" s="12" t="n">
         <v>1031</v>
       </c>
-      <c r="AU13" s="15">
+      <c r="AU13" s="13">
         <f>AT13/$D$13</f>
         <v/>
       </c>
-      <c r="AV13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 407 units, Block B: 376 units, Block C: 248 units</t>
+      <c r="AV13" s="14">
+        <f>AW13-AT13</f>
+        <v/>
+      </c>
+      <c r="AW13" s="14" t="n">
+        <v>1045</v>
+      </c>
+      <c r="AX13" s="15">
+        <f>AW13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 408 units, Block B: 380 units, Block C: 257 units</t>
         </is>
       </c>
     </row>
@@ -2354,20 +2458,31 @@
         <f>AQ14/$D$14</f>
         <v/>
       </c>
-      <c r="AS14" s="14">
+      <c r="AS14" s="12">
         <f>AT14-AQ14</f>
         <v/>
       </c>
-      <c r="AT14" s="14" t="n">
+      <c r="AT14" s="12" t="n">
         <v>785</v>
       </c>
-      <c r="AU14" s="15">
+      <c r="AU14" s="13">
         <f>AT14/$D$14</f>
         <v/>
       </c>
-      <c r="AV14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 510 units, Block B: 275 units</t>
+      <c r="AV14" s="14">
+        <f>AW14-AT14</f>
+        <v/>
+      </c>
+      <c r="AW14" s="14" t="n">
+        <v>797</v>
+      </c>
+      <c r="AX14" s="15">
+        <f>AW14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 516 units, Block B: 281 units</t>
         </is>
       </c>
     </row>
@@ -2531,20 +2646,31 @@
         <f>AQ15/$D$15</f>
         <v/>
       </c>
-      <c r="AS15" s="14">
+      <c r="AS15" s="12">
         <f>AT15-AQ15</f>
         <v/>
       </c>
-      <c r="AT15" s="14" t="n">
+      <c r="AT15" s="12" t="n">
         <v>1404</v>
       </c>
-      <c r="AU15" s="15">
+      <c r="AU15" s="13">
         <f>AT15/$D$15</f>
         <v/>
       </c>
-      <c r="AV15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 728 units, Block B: 676 units</t>
+      <c r="AV15" s="14">
+        <f>AW15-AT15</f>
+        <v/>
+      </c>
+      <c r="AW15" s="14" t="n">
+        <v>1409</v>
+      </c>
+      <c r="AX15" s="15">
+        <f>AW15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 731 units, Block B: 678 units</t>
         </is>
       </c>
     </row>
@@ -2708,18 +2834,29 @@
         <f>AQ16/$D$16</f>
         <v/>
       </c>
-      <c r="AS16" s="14">
+      <c r="AS16" s="12">
         <f>AT16-AQ16</f>
         <v/>
       </c>
-      <c r="AT16" s="14" t="n">
+      <c r="AT16" s="12" t="n">
         <v>916</v>
       </c>
-      <c r="AU16" s="15">
+      <c r="AU16" s="13">
         <f>AT16/$D$16</f>
         <v/>
       </c>
-      <c r="AV16" s="10" t="inlineStr">
+      <c r="AV16" s="14">
+        <f>AW16-AT16</f>
+        <v/>
+      </c>
+      <c r="AW16" s="14" t="n">
+        <v>917</v>
+      </c>
+      <c r="AX16" s="15">
+        <f>AW16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2843,10 +2980,13 @@
       <c r="AP17" s="12" t="n"/>
       <c r="AQ17" s="12" t="n"/>
       <c r="AR17" s="13" t="n"/>
-      <c r="AS17" s="14" t="n"/>
-      <c r="AT17" s="14" t="n"/>
-      <c r="AU17" s="15" t="n"/>
-      <c r="AV17" s="10" t="inlineStr">
+      <c r="AS17" s="12" t="n"/>
+      <c r="AT17" s="12" t="n"/>
+      <c r="AU17" s="13" t="n"/>
+      <c r="AV17" s="14" t="n"/>
+      <c r="AW17" s="14" t="n"/>
+      <c r="AX17" s="15" t="n"/>
+      <c r="AY17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3012,20 +3152,31 @@
         <f>AQ18/$D$18</f>
         <v/>
       </c>
-      <c r="AS18" s="14">
+      <c r="AS18" s="12">
         <f>AT18-AQ18</f>
         <v/>
       </c>
-      <c r="AT18" s="14" t="n">
+      <c r="AT18" s="12" t="n">
         <v>735</v>
       </c>
-      <c r="AU18" s="15">
+      <c r="AU18" s="13">
         <f>AT18/$D$18</f>
         <v/>
       </c>
-      <c r="AV18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 445 units, Block B: 290 units</t>
+      <c r="AV18" s="14">
+        <f>AW18-AT18</f>
+        <v/>
+      </c>
+      <c r="AW18" s="14" t="n">
+        <v>742</v>
+      </c>
+      <c r="AX18" s="15">
+        <f>AW18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AY18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 452 units, Block B: 290 units</t>
         </is>
       </c>
     </row>
@@ -3189,20 +3340,31 @@
         <f>AQ19/$D$19</f>
         <v/>
       </c>
-      <c r="AS19" s="14">
+      <c r="AS19" s="12">
         <f>AT19-AQ19</f>
         <v/>
       </c>
-      <c r="AT19" s="14" t="n">
+      <c r="AT19" s="12" t="n">
         <v>397</v>
       </c>
-      <c r="AU19" s="15">
+      <c r="AU19" s="13">
         <f>AT19/$D$19</f>
         <v/>
       </c>
-      <c r="AV19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 299 units, Block B: 98 units</t>
+      <c r="AV19" s="14">
+        <f>AW19-AT19</f>
+        <v/>
+      </c>
+      <c r="AW19" s="14" t="n">
+        <v>402</v>
+      </c>
+      <c r="AX19" s="15">
+        <f>AW19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AY19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 301 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -3366,20 +3528,31 @@
         <f>AQ20/$D$20</f>
         <v/>
       </c>
-      <c r="AS20" s="14">
+      <c r="AS20" s="12">
         <f>AT20-AQ20</f>
         <v/>
       </c>
-      <c r="AT20" s="14" t="n">
+      <c r="AT20" s="12" t="n">
         <v>325</v>
       </c>
-      <c r="AU20" s="15">
+      <c r="AU20" s="13">
         <f>AT20/$D$20</f>
         <v/>
       </c>
-      <c r="AV20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 222 units, Block B: 103 units</t>
+      <c r="AV20" s="14">
+        <f>AW20-AT20</f>
+        <v/>
+      </c>
+      <c r="AW20" s="14" t="n">
+        <v>331</v>
+      </c>
+      <c r="AX20" s="15">
+        <f>AW20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AY20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 227 units, Block B: 104 units</t>
         </is>
       </c>
     </row>
@@ -3447,21 +3620,32 @@
         <f>AQ21/$D$21</f>
         <v/>
       </c>
-      <c r="AS21" s="14">
+      <c r="AS21" s="12">
         <f>AT21-AQ21</f>
         <v/>
       </c>
-      <c r="AT21" s="14" t="n">
+      <c r="AT21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" s="15">
+      <c r="AU21" s="13">
         <f>AT21/$D$21</f>
         <v/>
       </c>
-      <c r="AV21" s="10" t="inlineStr"/>
+      <c r="AV21" s="14">
+        <f>AW21-AT21</f>
+        <v/>
+      </c>
+      <c r="AW21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="15">
+        <f>AW21/$D$21</f>
+        <v/>
+      </c>
+      <c r="AY21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
@@ -3476,6 +3660,7 @@
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="AM3:AO3"/>
     <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AV3:AX3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AY21"/>
+  <dimension ref="A2:BB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,10 @@
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
     <col width="9" customWidth="1" min="50" max="50"/>
-    <col width="46" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="52" max="52"/>
+    <col width="9" customWidth="1" min="53" max="53"/>
+    <col width="46" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -605,8 +608,11 @@
       <c r="AS3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="AV3" s="4" t="n">
+      <c r="AV3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -847,22 +853,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AV4" s="6" t="inlineStr">
+      <c r="AV4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AW4" s="6" t="inlineStr">
+      <c r="AW4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AX4" s="6" t="inlineStr">
+      <c r="AX4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AY4" s="5" t="inlineStr">
+      <c r="AY4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AZ4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BA4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="BB4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -924,6 +945,9 @@
       <c r="AW5" s="8" t="n"/>
       <c r="AX5" s="8" t="n"/>
       <c r="AY5" s="8" t="n"/>
+      <c r="AZ5" s="8" t="n"/>
+      <c r="BA5" s="8" t="n"/>
+      <c r="BB5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1096,20 +1120,31 @@
         <f>AT6/$D$6</f>
         <v/>
       </c>
-      <c r="AV6" s="14">
+      <c r="AV6" s="12">
         <f>AW6-AT6</f>
         <v/>
       </c>
-      <c r="AW6" s="14" t="n">
+      <c r="AW6" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="AX6" s="15">
+      <c r="AX6" s="13">
         <f>AW6/$D$6</f>
         <v/>
       </c>
-      <c r="AY6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 195 units, Block B: 126 units</t>
+      <c r="AY6" s="14">
+        <f>AZ6-AW6</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="14" t="n">
+        <v>328</v>
+      </c>
+      <c r="BA6" s="15">
+        <f>AZ6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BB6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 196 units, Block B: 132 units</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1319,31 @@
         <f>AT7/$D$7</f>
         <v/>
       </c>
-      <c r="AV7" s="14">
+      <c r="AV7" s="12">
         <f>AW7-AT7</f>
         <v/>
       </c>
-      <c r="AW7" s="14" t="n">
+      <c r="AW7" s="12" t="n">
         <v>1007</v>
       </c>
-      <c r="AX7" s="15">
+      <c r="AX7" s="13">
         <f>AW7/$D$7</f>
         <v/>
       </c>
-      <c r="AY7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 415 units, Block B: 391 units, Block C: 91 units, Block D: 110 units</t>
+      <c r="AY7" s="14">
+        <f>AZ7-AW7</f>
+        <v/>
+      </c>
+      <c r="AZ7" s="14" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BA7" s="15">
+        <f>AZ7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BB7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 417 units, Block B: 394 units, Block C: 92 units, Block D: 114 units</t>
         </is>
       </c>
     </row>
@@ -1472,18 +1518,29 @@
         <f>AT8/$D$8</f>
         <v/>
       </c>
-      <c r="AV8" s="14">
+      <c r="AV8" s="12">
         <f>AW8-AT8</f>
         <v/>
       </c>
-      <c r="AW8" s="14" t="n">
+      <c r="AW8" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="AX8" s="15">
+      <c r="AX8" s="13">
         <f>AW8/$D$8</f>
         <v/>
       </c>
-      <c r="AY8" s="10" t="inlineStr">
+      <c r="AY8" s="14">
+        <f>AZ8-AW8</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BA8" s="15">
+        <f>AZ8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BB8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1660,20 +1717,31 @@
         <f>AT9/$D$9</f>
         <v/>
       </c>
-      <c r="AV9" s="14">
+      <c r="AV9" s="12">
         <f>AW9-AT9</f>
         <v/>
       </c>
-      <c r="AW9" s="14" t="n">
+      <c r="AW9" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="AX9" s="15">
+      <c r="AX9" s="13">
         <f>AW9/$D$9</f>
         <v/>
       </c>
-      <c r="AY9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 671 units, Phase 2: 415 units</t>
+      <c r="AY9" s="14">
+        <f>AZ9-AW9</f>
+        <v/>
+      </c>
+      <c r="AZ9" s="14" t="n">
+        <v>1091</v>
+      </c>
+      <c r="BA9" s="15">
+        <f>AZ9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BB9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 420 units</t>
         </is>
       </c>
     </row>
@@ -1733,6 +1801,9 @@
       <c r="AW10" s="8" t="n"/>
       <c r="AX10" s="8" t="n"/>
       <c r="AY10" s="8" t="n"/>
+      <c r="AZ10" s="8" t="n"/>
+      <c r="BA10" s="8" t="n"/>
+      <c r="BB10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1905,18 +1976,29 @@
         <f>AT11/$D$11</f>
         <v/>
       </c>
-      <c r="AV11" s="14">
+      <c r="AV11" s="12">
         <f>AW11-AT11</f>
         <v/>
       </c>
-      <c r="AW11" s="14" t="n">
+      <c r="AW11" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="AX11" s="15">
+      <c r="AX11" s="13">
         <f>AW11/$D$11</f>
         <v/>
       </c>
-      <c r="AY11" s="10" t="inlineStr">
+      <c r="AY11" s="14">
+        <f>AZ11-AW11</f>
+        <v/>
+      </c>
+      <c r="AZ11" s="14" t="n">
+        <v>844</v>
+      </c>
+      <c r="BA11" s="15">
+        <f>AZ11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BB11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2093,20 +2175,31 @@
         <f>AT12/$D$12</f>
         <v/>
       </c>
-      <c r="AV12" s="14">
+      <c r="AV12" s="12">
         <f>AW12-AT12</f>
         <v/>
       </c>
-      <c r="AW12" s="14" t="n">
+      <c r="AW12" s="12" t="n">
         <v>1559</v>
       </c>
-      <c r="AX12" s="15">
+      <c r="AX12" s="13">
         <f>AW12/$D$12</f>
         <v/>
       </c>
-      <c r="AY12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 527 units, Block B: 538 units, Block D: 494 units</t>
+      <c r="AY12" s="14">
+        <f>AZ12-AW12</f>
+        <v/>
+      </c>
+      <c r="AZ12" s="14" t="n">
+        <v>1569</v>
+      </c>
+      <c r="BA12" s="15">
+        <f>AZ12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BB12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 533 units, Block B: 541 units, Block D: 495 units</t>
         </is>
       </c>
     </row>
@@ -2281,20 +2374,31 @@
         <f>AT13/$D$13</f>
         <v/>
       </c>
-      <c r="AV13" s="14">
+      <c r="AV13" s="12">
         <f>AW13-AT13</f>
         <v/>
       </c>
-      <c r="AW13" s="14" t="n">
+      <c r="AW13" s="12" t="n">
         <v>1045</v>
       </c>
-      <c r="AX13" s="15">
+      <c r="AX13" s="13">
         <f>AW13/$D$13</f>
         <v/>
       </c>
-      <c r="AY13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 408 units, Block B: 380 units, Block C: 257 units</t>
+      <c r="AY13" s="14">
+        <f>AZ13-AW13</f>
+        <v/>
+      </c>
+      <c r="AZ13" s="14" t="n">
+        <v>1064</v>
+      </c>
+      <c r="BA13" s="15">
+        <f>AZ13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BB13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 412 units, Block B: 384 units, Block C: 268 units</t>
         </is>
       </c>
     </row>
@@ -2469,20 +2573,31 @@
         <f>AT14/$D$14</f>
         <v/>
       </c>
-      <c r="AV14" s="14">
+      <c r="AV14" s="12">
         <f>AW14-AT14</f>
         <v/>
       </c>
-      <c r="AW14" s="14" t="n">
+      <c r="AW14" s="12" t="n">
         <v>797</v>
       </c>
-      <c r="AX14" s="15">
+      <c r="AX14" s="13">
         <f>AW14/$D$14</f>
         <v/>
       </c>
-      <c r="AY14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 516 units, Block B: 281 units</t>
+      <c r="AY14" s="14">
+        <f>AZ14-AW14</f>
+        <v/>
+      </c>
+      <c r="AZ14" s="14" t="n">
+        <v>813</v>
+      </c>
+      <c r="BA14" s="15">
+        <f>AZ14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BB14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 526 units, Block B: 287 units</t>
         </is>
       </c>
     </row>
@@ -2657,20 +2772,31 @@
         <f>AT15/$D$15</f>
         <v/>
       </c>
-      <c r="AV15" s="14">
+      <c r="AV15" s="12">
         <f>AW15-AT15</f>
         <v/>
       </c>
-      <c r="AW15" s="14" t="n">
+      <c r="AW15" s="12" t="n">
         <v>1409</v>
       </c>
-      <c r="AX15" s="15">
+      <c r="AX15" s="13">
         <f>AW15/$D$15</f>
         <v/>
       </c>
-      <c r="AY15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 731 units, Block B: 678 units</t>
+      <c r="AY15" s="14">
+        <f>AZ15-AW15</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="14" t="n">
+        <v>1415</v>
+      </c>
+      <c r="BA15" s="15">
+        <f>AZ15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BB15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 732 units, Block B: 683 units</t>
         </is>
       </c>
     </row>
@@ -2845,18 +2971,29 @@
         <f>AT16/$D$16</f>
         <v/>
       </c>
-      <c r="AV16" s="14">
+      <c r="AV16" s="12">
         <f>AW16-AT16</f>
         <v/>
       </c>
-      <c r="AW16" s="14" t="n">
+      <c r="AW16" s="12" t="n">
         <v>917</v>
       </c>
-      <c r="AX16" s="15">
+      <c r="AX16" s="13">
         <f>AW16/$D$16</f>
         <v/>
       </c>
-      <c r="AY16" s="10" t="inlineStr">
+      <c r="AY16" s="14">
+        <f>AZ16-AW16</f>
+        <v/>
+      </c>
+      <c r="AZ16" s="14" t="n">
+        <v>922</v>
+      </c>
+      <c r="BA16" s="15">
+        <f>AZ16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BB16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2983,10 +3120,13 @@
       <c r="AS17" s="12" t="n"/>
       <c r="AT17" s="12" t="n"/>
       <c r="AU17" s="13" t="n"/>
-      <c r="AV17" s="14" t="n"/>
-      <c r="AW17" s="14" t="n"/>
-      <c r="AX17" s="15" t="n"/>
-      <c r="AY17" s="10" t="inlineStr">
+      <c r="AV17" s="12" t="n"/>
+      <c r="AW17" s="12" t="n"/>
+      <c r="AX17" s="13" t="n"/>
+      <c r="AY17" s="14" t="n"/>
+      <c r="AZ17" s="14" t="n"/>
+      <c r="BA17" s="15" t="n"/>
+      <c r="BB17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3163,20 +3303,31 @@
         <f>AT18/$D$18</f>
         <v/>
       </c>
-      <c r="AV18" s="14">
+      <c r="AV18" s="12">
         <f>AW18-AT18</f>
         <v/>
       </c>
-      <c r="AW18" s="14" t="n">
+      <c r="AW18" s="12" t="n">
         <v>742</v>
       </c>
-      <c r="AX18" s="15">
+      <c r="AX18" s="13">
         <f>AW18/$D$18</f>
         <v/>
       </c>
-      <c r="AY18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 452 units, Block B: 290 units</t>
+      <c r="AY18" s="14">
+        <f>AZ18-AW18</f>
+        <v/>
+      </c>
+      <c r="AZ18" s="14" t="n">
+        <v>745</v>
+      </c>
+      <c r="BA18" s="15">
+        <f>AZ18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BB18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 455 units, Block B: 290 units</t>
         </is>
       </c>
     </row>
@@ -3351,20 +3502,31 @@
         <f>AT19/$D$19</f>
         <v/>
       </c>
-      <c r="AV19" s="14">
+      <c r="AV19" s="12">
         <f>AW19-AT19</f>
         <v/>
       </c>
-      <c r="AW19" s="14" t="n">
+      <c r="AW19" s="12" t="n">
         <v>402</v>
       </c>
-      <c r="AX19" s="15">
+      <c r="AX19" s="13">
         <f>AW19/$D$19</f>
         <v/>
       </c>
-      <c r="AY19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 301 units, Block B: 101 units</t>
+      <c r="AY19" s="14">
+        <f>AZ19-AW19</f>
+        <v/>
+      </c>
+      <c r="AZ19" s="14" t="n">
+        <v>407</v>
+      </c>
+      <c r="BA19" s="15">
+        <f>AZ19/$D$19</f>
+        <v/>
+      </c>
+      <c r="BB19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 301 units, Block B: 106 units</t>
         </is>
       </c>
     </row>
@@ -3539,20 +3701,31 @@
         <f>AT20/$D$20</f>
         <v/>
       </c>
-      <c r="AV20" s="14">
+      <c r="AV20" s="12">
         <f>AW20-AT20</f>
         <v/>
       </c>
-      <c r="AW20" s="14" t="n">
+      <c r="AW20" s="12" t="n">
         <v>331</v>
       </c>
-      <c r="AX20" s="15">
+      <c r="AX20" s="13">
         <f>AW20/$D$20</f>
         <v/>
       </c>
-      <c r="AY20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 227 units, Block B: 104 units</t>
+      <c r="AY20" s="14">
+        <f>AZ20-AW20</f>
+        <v/>
+      </c>
+      <c r="AZ20" s="14" t="n">
+        <v>333</v>
+      </c>
+      <c r="BA20" s="15">
+        <f>AZ20/$D$20</f>
+        <v/>
+      </c>
+      <c r="BB20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 227 units, Block B: 106 units</t>
         </is>
       </c>
     </row>
@@ -3631,21 +3804,33 @@
         <f>AT21/$D$21</f>
         <v/>
       </c>
-      <c r="AV21" s="14">
+      <c r="AV21" s="12">
         <f>AW21-AT21</f>
         <v/>
       </c>
-      <c r="AW21" s="14" t="n">
+      <c r="AW21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AX21" s="15">
+      <c r="AX21" s="13">
         <f>AW21/$D$21</f>
         <v/>
       </c>
-      <c r="AY21" s="10" t="inlineStr"/>
+      <c r="AY21" s="14">
+        <f>AZ21-AW21</f>
+        <v/>
+      </c>
+      <c r="AZ21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="15">
+        <f>AZ21/$D$21</f>
+        <v/>
+      </c>
+      <c r="BB21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="AY3:BA3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>

--- a/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BB21"/>
+  <dimension ref="A2:BE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,10 @@
     <col width="9" customWidth="1" min="51" max="51"/>
     <col width="9" customWidth="1" min="52" max="52"/>
     <col width="9" customWidth="1" min="53" max="53"/>
-    <col width="46" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="46" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -611,8 +614,11 @@
       <c r="AV3" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="AY3" s="3" t="n">
         <v>46297</v>
+      </c>
+      <c r="BB3" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -868,22 +874,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AY4" s="6" t="inlineStr">
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AZ4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BA4" s="6" t="inlineStr">
+      <c r="BA4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="BB4" s="5" t="inlineStr">
+      <c r="BB4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BC4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BD4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="BE4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -948,6 +969,9 @@
       <c r="AZ5" s="8" t="n"/>
       <c r="BA5" s="8" t="n"/>
       <c r="BB5" s="8" t="n"/>
+      <c r="BC5" s="8" t="n"/>
+      <c r="BD5" s="8" t="n"/>
+      <c r="BE5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1131,20 +1155,31 @@
         <f>AW6/$D$6</f>
         <v/>
       </c>
-      <c r="AY6" s="14">
+      <c r="AY6" s="12">
         <f>AZ6-AW6</f>
         <v/>
       </c>
-      <c r="AZ6" s="14" t="n">
+      <c r="AZ6" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="BA6" s="15">
+      <c r="BA6" s="13">
         <f>AZ6/$D$6</f>
         <v/>
       </c>
-      <c r="BB6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 196 units, Block B: 132 units</t>
+      <c r="BB6" s="14">
+        <f>BC6-AZ6</f>
+        <v/>
+      </c>
+      <c r="BC6" s="14" t="n">
+        <v>335</v>
+      </c>
+      <c r="BD6" s="15">
+        <f>BC6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 197 units, Block B: 138 units</t>
         </is>
       </c>
     </row>
@@ -1330,20 +1365,31 @@
         <f>AW7/$D$7</f>
         <v/>
       </c>
-      <c r="AY7" s="14">
+      <c r="AY7" s="12">
         <f>AZ7-AW7</f>
         <v/>
       </c>
-      <c r="AZ7" s="14" t="n">
+      <c r="AZ7" s="12" t="n">
         <v>1017</v>
       </c>
-      <c r="BA7" s="15">
+      <c r="BA7" s="13">
         <f>AZ7/$D$7</f>
         <v/>
       </c>
-      <c r="BB7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 417 units, Block B: 394 units, Block C: 92 units, Block D: 114 units</t>
+      <c r="BB7" s="14">
+        <f>BC7-AZ7</f>
+        <v/>
+      </c>
+      <c r="BC7" s="14" t="n">
+        <v>1025</v>
+      </c>
+      <c r="BD7" s="15">
+        <f>BC7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 422 units, Block B: 397 units, Block C: 92 units, Block D: 114 units</t>
         </is>
       </c>
     </row>
@@ -1529,18 +1575,29 @@
         <f>AW8/$D$8</f>
         <v/>
       </c>
-      <c r="AY8" s="14">
+      <c r="AY8" s="12">
         <f>AZ8-AW8</f>
         <v/>
       </c>
-      <c r="AZ8" s="14" t="n">
+      <c r="AZ8" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="BA8" s="15">
+      <c r="BA8" s="13">
         <f>AZ8/$D$8</f>
         <v/>
       </c>
-      <c r="BB8" s="10" t="inlineStr">
+      <c r="BB8" s="14">
+        <f>BC8-AZ8</f>
+        <v/>
+      </c>
+      <c r="BC8" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD8" s="15">
+        <f>BC8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1728,20 +1785,31 @@
         <f>AW9/$D$9</f>
         <v/>
       </c>
-      <c r="AY9" s="14">
+      <c r="AY9" s="12">
         <f>AZ9-AW9</f>
         <v/>
       </c>
-      <c r="AZ9" s="14" t="n">
+      <c r="AZ9" s="12" t="n">
         <v>1091</v>
       </c>
-      <c r="BA9" s="15">
+      <c r="BA9" s="13">
         <f>AZ9/$D$9</f>
         <v/>
       </c>
-      <c r="BB9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 671 units, Phase 2: 420 units</t>
+      <c r="BB9" s="14">
+        <f>BC9-AZ9</f>
+        <v/>
+      </c>
+      <c r="BC9" s="14" t="n">
+        <v>1096</v>
+      </c>
+      <c r="BD9" s="15">
+        <f>BC9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 425 units</t>
         </is>
       </c>
     </row>
@@ -1804,6 +1872,9 @@
       <c r="AZ10" s="8" t="n"/>
       <c r="BA10" s="8" t="n"/>
       <c r="BB10" s="8" t="n"/>
+      <c r="BC10" s="8" t="n"/>
+      <c r="BD10" s="8" t="n"/>
+      <c r="BE10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1987,18 +2058,29 @@
         <f>AW11/$D$11</f>
         <v/>
       </c>
-      <c r="AY11" s="14">
+      <c r="AY11" s="12">
         <f>AZ11-AW11</f>
         <v/>
       </c>
-      <c r="AZ11" s="14" t="n">
+      <c r="AZ11" s="12" t="n">
         <v>844</v>
       </c>
-      <c r="BA11" s="15">
+      <c r="BA11" s="13">
         <f>AZ11/$D$11</f>
         <v/>
       </c>
-      <c r="BB11" s="10" t="inlineStr">
+      <c r="BB11" s="14">
+        <f>BC11-AZ11</f>
+        <v/>
+      </c>
+      <c r="BC11" s="14" t="n">
+        <v>845</v>
+      </c>
+      <c r="BD11" s="15">
+        <f>BC11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2186,20 +2268,31 @@
         <f>AW12/$D$12</f>
         <v/>
       </c>
-      <c r="AY12" s="14">
+      <c r="AY12" s="12">
         <f>AZ12-AW12</f>
         <v/>
       </c>
-      <c r="AZ12" s="14" t="n">
+      <c r="AZ12" s="12" t="n">
         <v>1569</v>
       </c>
-      <c r="BA12" s="15">
+      <c r="BA12" s="13">
         <f>AZ12/$D$12</f>
         <v/>
       </c>
-      <c r="BB12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 533 units, Block B: 541 units, Block D: 495 units</t>
+      <c r="BB12" s="14">
+        <f>BC12-AZ12</f>
+        <v/>
+      </c>
+      <c r="BC12" s="14" t="n">
+        <v>1581</v>
+      </c>
+      <c r="BD12" s="15">
+        <f>BC12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 538 units, Block B: 546 units, Block D: 497 units</t>
         </is>
       </c>
     </row>
@@ -2385,20 +2478,31 @@
         <f>AW13/$D$13</f>
         <v/>
       </c>
-      <c r="AY13" s="14">
+      <c r="AY13" s="12">
         <f>AZ13-AW13</f>
         <v/>
       </c>
-      <c r="AZ13" s="14" t="n">
+      <c r="AZ13" s="12" t="n">
         <v>1064</v>
       </c>
-      <c r="BA13" s="15">
+      <c r="BA13" s="13">
         <f>AZ13/$D$13</f>
         <v/>
       </c>
-      <c r="BB13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 412 units, Block B: 384 units, Block C: 268 units</t>
+      <c r="BB13" s="14">
+        <f>BC13-AZ13</f>
+        <v/>
+      </c>
+      <c r="BC13" s="14" t="n">
+        <v>1074</v>
+      </c>
+      <c r="BD13" s="15">
+        <f>BC13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 414 units, Block B: 388 units, Block C: 272 units</t>
         </is>
       </c>
     </row>
@@ -2584,20 +2688,31 @@
         <f>AW14/$D$14</f>
         <v/>
       </c>
-      <c r="AY14" s="14">
+      <c r="AY14" s="12">
         <f>AZ14-AW14</f>
         <v/>
       </c>
-      <c r="AZ14" s="14" t="n">
+      <c r="AZ14" s="12" t="n">
         <v>813</v>
       </c>
-      <c r="BA14" s="15">
+      <c r="BA14" s="13">
         <f>AZ14/$D$14</f>
         <v/>
       </c>
-      <c r="BB14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 526 units, Block B: 287 units</t>
+      <c r="BB14" s="14">
+        <f>BC14-AZ14</f>
+        <v/>
+      </c>
+      <c r="BC14" s="14" t="n">
+        <v>831</v>
+      </c>
+      <c r="BD14" s="15">
+        <f>BC14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 533 units, Block B: 298 units</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2898,31 @@
         <f>AW15/$D$15</f>
         <v/>
       </c>
-      <c r="AY15" s="14">
+      <c r="AY15" s="12">
         <f>AZ15-AW15</f>
         <v/>
       </c>
-      <c r="AZ15" s="14" t="n">
+      <c r="AZ15" s="12" t="n">
         <v>1415</v>
       </c>
-      <c r="BA15" s="15">
+      <c r="BA15" s="13">
         <f>AZ15/$D$15</f>
         <v/>
       </c>
-      <c r="BB15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 732 units, Block B: 683 units</t>
+      <c r="BB15" s="14">
+        <f>BC15-AZ15</f>
+        <v/>
+      </c>
+      <c r="BC15" s="14" t="n">
+        <v>1419</v>
+      </c>
+      <c r="BD15" s="15">
+        <f>BC15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 734 units, Block B: 685 units</t>
         </is>
       </c>
     </row>
@@ -2982,18 +3108,29 @@
         <f>AW16/$D$16</f>
         <v/>
       </c>
-      <c r="AY16" s="14">
+      <c r="AY16" s="12">
         <f>AZ16-AW16</f>
         <v/>
       </c>
-      <c r="AZ16" s="14" t="n">
+      <c r="AZ16" s="12" t="n">
         <v>922</v>
       </c>
-      <c r="BA16" s="15">
+      <c r="BA16" s="13">
         <f>AZ16/$D$16</f>
         <v/>
       </c>
-      <c r="BB16" s="10" t="inlineStr">
+      <c r="BB16" s="14">
+        <f>BC16-AZ16</f>
+        <v/>
+      </c>
+      <c r="BC16" s="14" t="n">
+        <v>924</v>
+      </c>
+      <c r="BD16" s="15">
+        <f>BC16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3123,10 +3260,13 @@
       <c r="AV17" s="12" t="n"/>
       <c r="AW17" s="12" t="n"/>
       <c r="AX17" s="13" t="n"/>
-      <c r="AY17" s="14" t="n"/>
-      <c r="AZ17" s="14" t="n"/>
-      <c r="BA17" s="15" t="n"/>
-      <c r="BB17" s="10" t="inlineStr">
+      <c r="AY17" s="12" t="n"/>
+      <c r="AZ17" s="12" t="n"/>
+      <c r="BA17" s="13" t="n"/>
+      <c r="BB17" s="14" t="n"/>
+      <c r="BC17" s="14" t="n"/>
+      <c r="BD17" s="15" t="n"/>
+      <c r="BE17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3314,20 +3454,31 @@
         <f>AW18/$D$18</f>
         <v/>
       </c>
-      <c r="AY18" s="14">
+      <c r="AY18" s="12">
         <f>AZ18-AW18</f>
         <v/>
       </c>
-      <c r="AZ18" s="14" t="n">
+      <c r="AZ18" s="12" t="n">
         <v>745</v>
       </c>
-      <c r="BA18" s="15">
+      <c r="BA18" s="13">
         <f>AZ18/$D$18</f>
         <v/>
       </c>
-      <c r="BB18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 455 units, Block B: 290 units</t>
+      <c r="BB18" s="14">
+        <f>BC18-AZ18</f>
+        <v/>
+      </c>
+      <c r="BC18" s="14" t="n">
+        <v>749</v>
+      </c>
+      <c r="BD18" s="15">
+        <f>BC18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BE18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 457 units, Block B: 292 units</t>
         </is>
       </c>
     </row>
@@ -3513,20 +3664,31 @@
         <f>AW19/$D$19</f>
         <v/>
       </c>
-      <c r="AY19" s="14">
+      <c r="AY19" s="12">
         <f>AZ19-AW19</f>
         <v/>
       </c>
-      <c r="AZ19" s="14" t="n">
+      <c r="AZ19" s="12" t="n">
         <v>407</v>
       </c>
-      <c r="BA19" s="15">
+      <c r="BA19" s="13">
         <f>AZ19/$D$19</f>
         <v/>
       </c>
-      <c r="BB19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 301 units, Block B: 106 units</t>
+      <c r="BB19" s="14">
+        <f>BC19-AZ19</f>
+        <v/>
+      </c>
+      <c r="BC19" s="14" t="n">
+        <v>409</v>
+      </c>
+      <c r="BD19" s="15">
+        <f>BC19/$D$19</f>
+        <v/>
+      </c>
+      <c r="BE19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 302 units, Block B: 107 units</t>
         </is>
       </c>
     </row>
@@ -3712,20 +3874,31 @@
         <f>AW20/$D$20</f>
         <v/>
       </c>
-      <c r="AY20" s="14">
+      <c r="AY20" s="12">
         <f>AZ20-AW20</f>
         <v/>
       </c>
-      <c r="AZ20" s="14" t="n">
+      <c r="AZ20" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="BA20" s="15">
+      <c r="BA20" s="13">
         <f>AZ20/$D$20</f>
         <v/>
       </c>
-      <c r="BB20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 227 units, Block B: 106 units</t>
+      <c r="BB20" s="14">
+        <f>BC20-AZ20</f>
+        <v/>
+      </c>
+      <c r="BC20" s="14" t="n">
+        <v>341</v>
+      </c>
+      <c r="BD20" s="15">
+        <f>BC20/$D$20</f>
+        <v/>
+      </c>
+      <c r="BE20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 229 units, Block B: 112 units</t>
         </is>
       </c>
     </row>
@@ -3815,22 +3988,34 @@
         <f>AW21/$D$21</f>
         <v/>
       </c>
-      <c r="AY21" s="14">
+      <c r="AY21" s="12">
         <f>AZ21-AW21</f>
         <v/>
       </c>
-      <c r="AZ21" s="14" t="n">
+      <c r="AZ21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="BA21" s="15">
+      <c r="BA21" s="13">
         <f>AZ21/$D$21</f>
         <v/>
       </c>
-      <c r="BB21" s="10" t="inlineStr"/>
+      <c r="BB21" s="14">
+        <f>BC21-AZ21</f>
+        <v/>
+      </c>
+      <c r="BC21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="15">
+        <f>BC21/$D$21</f>
+        <v/>
+      </c>
+      <c r="BE21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
